--- a/DocBusinessThienAn/BaoCaoTuanITS15/PCN_WeeklyReport_20261012.xlsx
+++ b/DocBusinessThienAn/BaoCaoTuanITS15/PCN_WeeklyReport_20261012.xlsx
@@ -287,24 +287,15 @@
   </si>
   <si>
     <t>Phân hệ Chia sẻ Dữ liệu (ShareData - ESHARE):
-- Xây dựng Visual Query Builder và tùy biến truy vấn SQL trích xuất động cho các gói tin, hỗ trợ đầy đủ các tham số hóa hệ thống.
-- Bỏ bảng trung gian ShareDataPacketExtractSql, gom trực tiếp câu lệnh SQL vào cấu hình gói tin (ExtractSql).
-- Chuyển đổi cơ chế lưu vết cấu hình động sang chuẩn SysOpConfig (ShareDataTracker), loại bỏ hàm tạo bảng động EnsureTablesCreated.
-- Chuẩn hóa toàn bộ kịch bản CSDL thành bộ script phân loại theo vai trò (00 đến 05).
-- Hoàn thiện và thông luồng dữ liệu trích xuất cho gói tin 110 (Thông điệp cộng đồng / VMS).
-- Tách tầng kết nối, giao thức truyền tải sang thư viện riêng Modules.Integration.ShareData dùng chung giữa WebAPI và Worker.
-Phân hệ Tường màn hình (VideoWall):
-- Tối ưu hóa giao tiếp thiết bị điều khiển phần cứng Hikvision (ISAPI Controller) qua NATS, chống nghẽn WebAPI.
-- Hoàn thiện ứng dụng WPF kết nối trực quan ma trận tường màn hình và điều khiển thiết bị.</t>
+- Xây dựng tính năng tạo và tùy biến câu truy vấn trích xuất dữ liệu động.
+- Tích hợp trực tiếp câu lệnh trích xuất dữ liệu động vào cấu hình gói tin và ánh xạ đối tác.
+- Tách độc lập tầng kết nối và điều phối giao thức truyền tải (WebAPI, Kafka, FTP) dùng chung cho toàn hệ thống.</t>
   </si>
   <si>
     <t>Phân hệ Chia sẻ Dữ liệu (ShareData):
-- Kiểm thử tích hợp đa đối tác, tối ưu hiệu năng Change Tracking và đồng bộ dữ liệu thời gian thực trên môi trường nội bộ.
-- Vận hành thử nghiệm tầng kết nối Modules.Integration.ShareData trên các giao thức WebAPI, Kafka và FTP.
-- Hỗ trợ và phối hợp kiểm thử sau đợt tái cấu trúc.
-Phân hệ Tường màn hình (VideoWall):
-- Tiếp tục hoàn thiện ứng dụng điều khiển WPF và tinh chỉnh các kịch bản chuyển Scene, quản lý bố cục ma trận màn hình.
-- Tối ưu hóa độ trễ phản hồi trạng thái thiết bị qua NATS.</t>
+- Theo dõi và khắc phục các vấn đề phát sinh theo yêu cầu XD006.7.1.
+- Xây dựng kịch bản kiểm thử và nghiệm thu chức năng chia sẻ dữ liệu.
+- Kiểm thử tích hợp kết nối và đồng bộ dữ liệu thời gian thực trên môi trường nội bộ.</t>
   </si>
 </sst>
 </file>
@@ -1249,7 +1240,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -2016,7 +2007,7 @@
       <c r="O31" s="52"/>
       <c r="P31" s="2"/>
     </row>
-    <row r="32" spans="1:16" ht="340" customHeight="1">
+    <row r="32" spans="1:16" ht="180" customHeight="1">
       <c r="A32" s="57">
         <v>1</v>
       </c>
@@ -2058,7 +2049,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="33" spans="1:16" ht="190" customHeight="1">
+    <row r="33" spans="1:16" ht="180" customHeight="1">
       <c r="A33" s="84">
         <v>2</v>
       </c>
@@ -2189,7 +2180,7 @@
       <c r="F40" s="2"/>
     </row>
   </sheetData>
-  <autoFilter ref="A7:O34" ns2:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A7:O34" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="22">
     <mergeCell ref="J33:J34"/>
     <mergeCell ref="K33:K34"/>
@@ -2215,8 +2206,8 @@
     <mergeCell ref="B7:D7"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="P33" ns3:id="rId1" ns2:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="P32" ns3:id="rId2" ns2:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="P33" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="P32" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
   </hyperlinks>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.59055118110236204" right="0.59055118110236204" top="0.59055118110236204" bottom="0.59055118110236204" header="0.196850393700787" footer="0.196850393700787"/>
@@ -2225,7 +2216,7 @@
     <oddHeader>&amp;L&amp;"+,Italic"&amp;8&amp;K7030A0WEEKLY REPORT</oddHeader>
     <oddFooter>&amp;R&amp;"+,Italic"&amp;8&amp;K7030A0Page &amp;P of &amp;N</oddFooter>
   </headerFooter>
-  <drawing ns3:id="rId3"/>
+  <drawing r:id="rId3"/>
 </worksheet>
 </file>
 
